--- a/data/trans_camb/IP19C04-Dificultad-trans_camb.xlsx
+++ b/data/trans_camb/IP19C04-Dificultad-trans_camb.xlsx
@@ -40,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -66,13 +66,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
@@ -513,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -524,9 +517,6 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -542,68 +532,50 @@
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
-      <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Niña</t>
         </is>
       </c>
-      <c r="G1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
       <c r="B2" s="2" t="n"/>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>2012/2007</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2016/2007</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2023/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
     </row>
@@ -616,9 +588,6 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -631,15 +600,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr"/>
-      <c r="D4" s="5" t="inlineStr"/>
-      <c r="E4" s="5" t="inlineStr"/>
-      <c r="F4" s="5" t="inlineStr"/>
-      <c r="G4" s="5" t="inlineStr"/>
-      <c r="H4" s="5" t="inlineStr"/>
-      <c r="I4" s="5" t="inlineStr"/>
-      <c r="J4" s="5" t="inlineStr"/>
-      <c r="K4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="n">
+        <v>0.05497029595262909</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-2.042784850570216</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-0.918125920924353</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-0.6664231718490593</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>-0.4476025097594615</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>-1.443233003557472</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
@@ -648,15 +626,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr"/>
-      <c r="D5" s="5" t="inlineStr"/>
-      <c r="E5" s="5" t="inlineStr"/>
-      <c r="F5" s="5" t="inlineStr"/>
-      <c r="G5" s="5" t="inlineStr"/>
-      <c r="H5" s="5" t="inlineStr"/>
-      <c r="I5" s="5" t="inlineStr"/>
-      <c r="J5" s="5" t="inlineStr"/>
-      <c r="K5" s="5" t="inlineStr"/>
+      <c r="C5" s="5" t="n">
+        <v>-4.950199706670105</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-6.631986010837881</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-6.323807761456843</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-6.643184480111966</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>-4.329029336872304</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>-5.4932001372052</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
@@ -665,15 +652,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr"/>
-      <c r="D6" s="5" t="inlineStr"/>
-      <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr"/>
-      <c r="J6" s="5" t="inlineStr"/>
-      <c r="K6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="n">
+        <v>4.481700953951424</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>4.522917171772459</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>3.803121647663939</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>8.205870260526051</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>2.831797739023011</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>3.34084886731309</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
@@ -682,15 +678,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr"/>
-      <c r="D7" s="6" t="inlineStr"/>
-      <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="6" t="inlineStr"/>
-      <c r="H7" s="6" t="inlineStr"/>
-      <c r="I7" s="6" t="inlineStr"/>
-      <c r="J7" s="6" t="inlineStr"/>
-      <c r="K7" s="6" t="inlineStr"/>
+      <c r="C7" s="6" t="n">
+        <v>0.01116402054209773</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>-0.4148730080424681</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>-0.1387499636962362</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>-0.1007118836240831</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.07744781333265531</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.2497198693437036</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
@@ -699,15 +704,22 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr"/>
+      <c r="C8" s="6" t="n">
+        <v>-0.6425254766241945</v>
+      </c>
       <c r="D8" s="6" t="inlineStr"/>
-      <c r="E8" s="6" t="inlineStr"/>
-      <c r="F8" s="6" t="inlineStr"/>
-      <c r="G8" s="6" t="inlineStr"/>
-      <c r="H8" s="6" t="inlineStr"/>
-      <c r="I8" s="6" t="inlineStr"/>
-      <c r="J8" s="6" t="inlineStr"/>
-      <c r="K8" s="6" t="inlineStr"/>
+      <c r="E8" s="6" t="n">
+        <v>-0.6630578648897963</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>-0.7991248619549282</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.5527878170845462</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.7694545403409929</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
@@ -716,15 +728,22 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr"/>
+      <c r="C9" s="6" t="n">
+        <v>2.251851710971664</v>
+      </c>
       <c r="D9" s="6" t="inlineStr"/>
-      <c r="E9" s="6" t="inlineStr"/>
-      <c r="F9" s="6" t="inlineStr"/>
-      <c r="G9" s="6" t="inlineStr"/>
-      <c r="H9" s="6" t="inlineStr"/>
-      <c r="I9" s="6" t="inlineStr"/>
-      <c r="J9" s="6" t="inlineStr"/>
-      <c r="K9" s="6" t="inlineStr"/>
+      <c r="E9" s="6" t="n">
+        <v>1.032137473424661</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>2.03309750942559</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.7138752007280514</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.8026572520192262</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -737,15 +756,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr"/>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="inlineStr"/>
-      <c r="F10" s="5" t="inlineStr"/>
-      <c r="G10" s="5" t="inlineStr"/>
-      <c r="H10" s="5" t="inlineStr"/>
-      <c r="I10" s="5" t="inlineStr"/>
-      <c r="J10" s="5" t="inlineStr"/>
-      <c r="K10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="n">
+        <v>-2.063721963397779</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-4.993921340211916</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-0.5735862798527745</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-0.5507005583415054</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>-1.388778426206746</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>-2.885668227702907</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
@@ -754,15 +782,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr"/>
-      <c r="D11" s="5" t="inlineStr"/>
-      <c r="E11" s="5" t="inlineStr"/>
-      <c r="F11" s="5" t="inlineStr"/>
-      <c r="G11" s="5" t="inlineStr"/>
-      <c r="H11" s="5" t="inlineStr"/>
-      <c r="I11" s="5" t="inlineStr"/>
-      <c r="J11" s="5" t="inlineStr"/>
-      <c r="K11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="n">
+        <v>-7.571546754287492</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-10.20650939924036</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-4.82189437840274</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-4.909680739762388</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>-4.720982039331322</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>-5.740724283358261</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
@@ -771,15 +808,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr"/>
-      <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="5" t="inlineStr"/>
-      <c r="F12" s="5" t="inlineStr"/>
-      <c r="G12" s="5" t="inlineStr"/>
-      <c r="H12" s="5" t="inlineStr"/>
-      <c r="I12" s="5" t="inlineStr"/>
-      <c r="J12" s="5" t="inlineStr"/>
-      <c r="K12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="n">
+        <v>3.248438405209579</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>-0.598086968273752</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>4.559727783475421</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>4.339542346320627</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>2.263083334090936</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>0.1930771319533344</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
@@ -788,15 +834,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr"/>
-      <c r="D13" s="6" t="inlineStr"/>
-      <c r="E13" s="6" t="inlineStr"/>
-      <c r="F13" s="6" t="inlineStr"/>
-      <c r="G13" s="6" t="inlineStr"/>
-      <c r="H13" s="6" t="inlineStr"/>
-      <c r="I13" s="6" t="inlineStr"/>
-      <c r="J13" s="6" t="inlineStr"/>
-      <c r="K13" s="6" t="inlineStr"/>
+      <c r="C13" s="6" t="n">
+        <v>-0.2962427883229096</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>-0.7168665201652967</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>-0.1272784578611407</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>-0.1222001297293355</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.240103509993001</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.4988982094423788</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
@@ -805,15 +860,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr"/>
-      <c r="D14" s="6" t="inlineStr"/>
-      <c r="E14" s="6" t="inlineStr"/>
-      <c r="F14" s="6" t="inlineStr"/>
-      <c r="G14" s="6" t="inlineStr"/>
-      <c r="H14" s="6" t="inlineStr"/>
-      <c r="I14" s="6" t="inlineStr"/>
-      <c r="J14" s="6" t="inlineStr"/>
-      <c r="K14" s="6" t="inlineStr"/>
+      <c r="C14" s="6" t="n">
+        <v>-0.7652948093024649</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>-0.7349352392006976</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>-0.7800838799581468</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.653361510543779</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.7543140959356653</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
@@ -822,15 +886,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr"/>
-      <c r="D15" s="6" t="inlineStr"/>
-      <c r="E15" s="6" t="inlineStr"/>
-      <c r="F15" s="6" t="inlineStr"/>
-      <c r="G15" s="6" t="inlineStr"/>
-      <c r="H15" s="6" t="inlineStr"/>
-      <c r="I15" s="6" t="inlineStr"/>
-      <c r="J15" s="6" t="inlineStr"/>
-      <c r="K15" s="6" t="inlineStr"/>
+      <c r="C15" s="6" t="n">
+        <v>0.8419725720265365</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>0.147327431183593</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>2.485475062918502</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>2.114045248811177</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.6069945024554588</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.1313248485727249</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -843,15 +916,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr"/>
-      <c r="D16" s="5" t="inlineStr"/>
-      <c r="E16" s="5" t="inlineStr"/>
-      <c r="F16" s="5" t="inlineStr"/>
-      <c r="G16" s="5" t="inlineStr"/>
-      <c r="H16" s="5" t="inlineStr"/>
-      <c r="I16" s="5" t="inlineStr"/>
-      <c r="J16" s="5" t="inlineStr"/>
-      <c r="K16" s="5" t="inlineStr"/>
+      <c r="C16" s="5" t="n">
+        <v>-2.771576476737635</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-1.624662209513102</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-2.931533938092091</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-4.247812576597363</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>-2.849978639740967</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>-2.769219892639287</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
@@ -860,15 +942,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr"/>
-      <c r="D17" s="5" t="inlineStr"/>
-      <c r="E17" s="5" t="inlineStr"/>
-      <c r="F17" s="5" t="inlineStr"/>
-      <c r="G17" s="5" t="inlineStr"/>
-      <c r="H17" s="5" t="inlineStr"/>
-      <c r="I17" s="5" t="inlineStr"/>
-      <c r="J17" s="5" t="inlineStr"/>
-      <c r="K17" s="5" t="inlineStr"/>
+      <c r="C17" s="5" t="n">
+        <v>-7.63689111812888</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-7.491875938864235</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-8.485043962776077</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-9.726379536336035</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>-6.350653426169788</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>-6.647432218084664</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
@@ -877,15 +968,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr"/>
-      <c r="D18" s="5" t="inlineStr"/>
-      <c r="E18" s="5" t="inlineStr"/>
-      <c r="F18" s="5" t="inlineStr"/>
-      <c r="G18" s="5" t="inlineStr"/>
-      <c r="H18" s="5" t="inlineStr"/>
-      <c r="I18" s="5" t="inlineStr"/>
-      <c r="J18" s="5" t="inlineStr"/>
-      <c r="K18" s="5" t="inlineStr"/>
+      <c r="C18" s="5" t="n">
+        <v>1.683291550218145</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>2.367974645680914</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>1.51514504672319</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>-0.4858392685716456</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>0.3484028206902385</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>0.04828814829252032</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n"/>
@@ -894,15 +994,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr"/>
-      <c r="D19" s="6" t="inlineStr"/>
-      <c r="E19" s="6" t="inlineStr"/>
-      <c r="F19" s="6" t="inlineStr"/>
-      <c r="G19" s="6" t="inlineStr"/>
-      <c r="H19" s="6" t="inlineStr"/>
-      <c r="I19" s="6" t="inlineStr"/>
-      <c r="J19" s="6" t="inlineStr"/>
-      <c r="K19" s="6" t="inlineStr"/>
+      <c r="C19" s="6" t="n">
+        <v>-0.5168963948335348</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>-0.3029979673907816</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>-0.5390159868793798</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>-0.7810378240217195</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>-0.5278558581448893</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>-0.5128982099858357</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n"/>
@@ -911,15 +1020,22 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr"/>
-      <c r="D20" s="6" t="inlineStr"/>
-      <c r="E20" s="6" t="inlineStr"/>
+      <c r="C20" s="6" t="n">
+        <v>-0.9889255449165942</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>-0.8093741084934691</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>-1</v>
+      </c>
       <c r="F20" s="6" t="inlineStr"/>
-      <c r="G20" s="6" t="inlineStr"/>
-      <c r="H20" s="6" t="inlineStr"/>
-      <c r="I20" s="6" t="inlineStr"/>
-      <c r="J20" s="6" t="inlineStr"/>
-      <c r="K20" s="6" t="inlineStr"/>
+      <c r="G20" s="6" t="n">
+        <v>-0.8422472111054593</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>-0.8138536867869214</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n"/>
@@ -928,15 +1044,22 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr"/>
-      <c r="D21" s="6" t="inlineStr"/>
-      <c r="E21" s="6" t="inlineStr"/>
+      <c r="C21" s="6" t="n">
+        <v>0.9668577986827189</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>0.9873162793620714</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>1.146084441401935</v>
+      </c>
       <c r="F21" s="6" t="inlineStr"/>
-      <c r="G21" s="6" t="inlineStr"/>
-      <c r="H21" s="6" t="inlineStr"/>
-      <c r="I21" s="6" t="inlineStr"/>
-      <c r="J21" s="6" t="inlineStr"/>
-      <c r="K21" s="6" t="inlineStr"/>
+      <c r="G21" s="6" t="n">
+        <v>0.3346471194958628</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>0.0445362279461976</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -949,15 +1072,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr"/>
-      <c r="D22" s="5" t="inlineStr"/>
-      <c r="E22" s="5" t="inlineStr"/>
-      <c r="F22" s="5" t="inlineStr"/>
-      <c r="G22" s="5" t="inlineStr"/>
-      <c r="H22" s="5" t="inlineStr"/>
-      <c r="I22" s="5" t="inlineStr"/>
-      <c r="J22" s="5" t="inlineStr"/>
-      <c r="K22" s="5" t="inlineStr"/>
+      <c r="C22" s="5" t="n">
+        <v>-2.866634044700155</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>-0.7868026556655541</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>-0.8648688382564579</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>-1.435029790323977</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>-1.948684029785665</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>-1.060423622260159</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n"/>
@@ -966,15 +1098,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr"/>
-      <c r="D23" s="5" t="inlineStr"/>
-      <c r="E23" s="5" t="inlineStr"/>
-      <c r="F23" s="5" t="inlineStr"/>
-      <c r="G23" s="5" t="inlineStr"/>
-      <c r="H23" s="5" t="inlineStr"/>
-      <c r="I23" s="5" t="inlineStr"/>
-      <c r="J23" s="5" t="inlineStr"/>
-      <c r="K23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="n">
+        <v>-9.095778077254076</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-8.142930174071147</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-12.38533868922373</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-11.8507944128202</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>-7.844163119550342</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>-7.863398502577619</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n"/>
@@ -983,15 +1124,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr"/>
-      <c r="D24" s="5" t="inlineStr"/>
-      <c r="E24" s="5" t="inlineStr"/>
-      <c r="F24" s="5" t="inlineStr"/>
-      <c r="G24" s="5" t="inlineStr"/>
-      <c r="H24" s="5" t="inlineStr"/>
-      <c r="I24" s="5" t="inlineStr"/>
-      <c r="J24" s="5" t="inlineStr"/>
-      <c r="K24" s="5" t="inlineStr"/>
+      <c r="C24" s="5" t="n">
+        <v>2.101159728117952</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>4.198405968895917</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>9.225588236483183</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>7.211504340910681</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>3.888522934138032</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>3.58002199183951</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n"/>
@@ -1000,15 +1150,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr"/>
-      <c r="D25" s="6" t="inlineStr"/>
-      <c r="E25" s="6" t="inlineStr"/>
-      <c r="F25" s="6" t="inlineStr"/>
-      <c r="G25" s="6" t="inlineStr"/>
-      <c r="H25" s="6" t="inlineStr"/>
-      <c r="I25" s="6" t="inlineStr"/>
-      <c r="J25" s="6" t="inlineStr"/>
-      <c r="K25" s="6" t="inlineStr"/>
+      <c r="C25" s="6" t="n">
+        <v>-0.6308381069224172</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>-0.1731456091297156</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>-0.08320235531369134</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>-0.1380531396425023</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>-0.2683766642000494</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>-0.1460436633292555</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n"/>
@@ -1019,13 +1178,18 @@
       </c>
       <c r="C26" s="6" t="inlineStr"/>
       <c r="D26" s="6" t="inlineStr"/>
-      <c r="E26" s="6" t="inlineStr"/>
-      <c r="F26" s="6" t="inlineStr"/>
-      <c r="G26" s="6" t="inlineStr"/>
-      <c r="H26" s="6" t="inlineStr"/>
-      <c r="I26" s="6" t="inlineStr"/>
-      <c r="J26" s="6" t="inlineStr"/>
-      <c r="K26" s="6" t="inlineStr"/>
+      <c r="E26" s="6" t="n">
+        <v>-0.7617730465595447</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>-0.6861661735192867</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>-0.7765765244208738</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>-0.6551863308883259</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n"/>
@@ -1036,13 +1200,18 @@
       </c>
       <c r="C27" s="6" t="inlineStr"/>
       <c r="D27" s="6" t="inlineStr"/>
-      <c r="E27" s="6" t="inlineStr"/>
-      <c r="F27" s="6" t="inlineStr"/>
-      <c r="G27" s="6" t="inlineStr"/>
-      <c r="H27" s="6" t="inlineStr"/>
-      <c r="I27" s="6" t="inlineStr"/>
-      <c r="J27" s="6" t="inlineStr"/>
-      <c r="K27" s="6" t="inlineStr"/>
+      <c r="E27" s="6" t="n">
+        <v>2.211858136244858</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>1.992221926320398</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>1.28998223471478</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>0.9401298713240654</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -1055,15 +1224,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr"/>
-      <c r="D28" s="5" t="inlineStr"/>
-      <c r="E28" s="5" t="inlineStr"/>
-      <c r="F28" s="5" t="inlineStr"/>
-      <c r="G28" s="5" t="inlineStr"/>
-      <c r="H28" s="5" t="inlineStr"/>
-      <c r="I28" s="5" t="inlineStr"/>
-      <c r="J28" s="5" t="inlineStr"/>
-      <c r="K28" s="5" t="inlineStr"/>
+      <c r="C28" s="5" t="n">
+        <v>-1.673326928655215</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>-2.485671443945916</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>-1.136551118465236</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>-1.587681766262876</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>-1.402708175714686</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>-2.09005305923892</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n"/>
@@ -1072,15 +1250,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr"/>
-      <c r="D29" s="5" t="inlineStr"/>
-      <c r="E29" s="5" t="inlineStr"/>
-      <c r="F29" s="5" t="inlineStr"/>
-      <c r="G29" s="5" t="inlineStr"/>
-      <c r="H29" s="5" t="inlineStr"/>
-      <c r="I29" s="5" t="inlineStr"/>
-      <c r="J29" s="5" t="inlineStr"/>
-      <c r="K29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="n">
+        <v>-4.518996842979509</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>-5.087900834342051</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>-4.340845318609208</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>-4.30327319514002</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>-3.458090894160822</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>-3.99489583327203</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n"/>
@@ -1089,15 +1276,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr"/>
-      <c r="D30" s="5" t="inlineStr"/>
-      <c r="E30" s="5" t="inlineStr"/>
-      <c r="F30" s="5" t="inlineStr"/>
-      <c r="G30" s="5" t="inlineStr"/>
-      <c r="H30" s="5" t="inlineStr"/>
-      <c r="I30" s="5" t="inlineStr"/>
-      <c r="J30" s="5" t="inlineStr"/>
-      <c r="K30" s="5" t="inlineStr"/>
+      <c r="C30" s="5" t="n">
+        <v>0.99909659193657</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>-0.09836147931794714</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>1.438594040063967</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>1.006720231213997</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>0.5499003463558232</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>-0.1899268074617339</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n"/>
@@ -1106,15 +1302,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr"/>
-      <c r="D31" s="6" t="inlineStr"/>
-      <c r="E31" s="6" t="inlineStr"/>
-      <c r="F31" s="6" t="inlineStr"/>
-      <c r="G31" s="6" t="inlineStr"/>
-      <c r="H31" s="6" t="inlineStr"/>
-      <c r="I31" s="6" t="inlineStr"/>
-      <c r="J31" s="6" t="inlineStr"/>
-      <c r="K31" s="6" t="inlineStr"/>
+      <c r="C31" s="6" t="n">
+        <v>-0.2971528112299305</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>-0.4414106082402513</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>-0.1856424405516836</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>-0.2593293984932744</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>-0.2389358963632553</v>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>-0.3560175308036361</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n"/>
@@ -1123,15 +1328,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr"/>
-      <c r="D32" s="6" t="inlineStr"/>
-      <c r="E32" s="6" t="inlineStr"/>
-      <c r="F32" s="6" t="inlineStr"/>
-      <c r="G32" s="6" t="inlineStr"/>
-      <c r="H32" s="6" t="inlineStr"/>
-      <c r="I32" s="6" t="inlineStr"/>
-      <c r="J32" s="6" t="inlineStr"/>
-      <c r="K32" s="6" t="inlineStr"/>
+      <c r="C32" s="6" t="n">
+        <v>-0.6088180188869318</v>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>-0.7030161624235499</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>-0.5464820683396263</v>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>-0.568725502933877</v>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>-0.4874656845436202</v>
+      </c>
+      <c r="H32" s="6" t="n">
+        <v>-0.5653732181167348</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n"/>
@@ -1140,15 +1354,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr"/>
-      <c r="D33" s="6" t="inlineStr"/>
-      <c r="E33" s="6" t="inlineStr"/>
-      <c r="F33" s="6" t="inlineStr"/>
-      <c r="G33" s="6" t="inlineStr"/>
-      <c r="H33" s="6" t="inlineStr"/>
-      <c r="I33" s="6" t="inlineStr"/>
-      <c r="J33" s="6" t="inlineStr"/>
-      <c r="K33" s="6" t="inlineStr"/>
+      <c r="C33" s="6" t="n">
+        <v>0.2661439691202429</v>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>-0.004557021751118091</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>0.3342590714126571</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>0.2253316253552793</v>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v>0.1230360445636444</v>
+      </c>
+      <c r="H33" s="6" t="n">
+        <v>-0.02619465597479673</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1159,11 +1382,11 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="C1:E1"/>
     <mergeCell ref="A22:A27"/>
     <mergeCell ref="A4:A9"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="E1:F1"/>
     <mergeCell ref="A16:A21"/>
     <mergeCell ref="A10:A15"/>
     <mergeCell ref="A28:A33"/>
